--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M594"/>
+  <dimension ref="A1:M595"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24759,6 +24759,47 @@
         <v>255.7</v>
       </c>
     </row>
+    <row r="595" spans="1:13">
+      <c r="A595" s="1">
+        <v>46272</v>
+      </c>
+      <c r="B595">
+        <v>226.7</v>
+      </c>
+      <c r="C595">
+        <v>255.7</v>
+      </c>
+      <c r="D595">
+        <v>215.4</v>
+      </c>
+      <c r="E595">
+        <v>215.4</v>
+      </c>
+      <c r="F595">
+        <v>227.6</v>
+      </c>
+      <c r="G595">
+        <v>262.4</v>
+      </c>
+      <c r="H595">
+        <v>226.9</v>
+      </c>
+      <c r="I595">
+        <v>255.8</v>
+      </c>
+      <c r="J595">
+        <v>248.7</v>
+      </c>
+      <c r="K595">
+        <v>257.6</v>
+      </c>
+      <c r="L595">
+        <v>226.6</v>
+      </c>
+      <c r="M595">
+        <v>255.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M595"/>
+  <dimension ref="A1:M596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24800,6 +24800,47 @@
         <v>255.7</v>
       </c>
     </row>
+    <row r="596" spans="1:13">
+      <c r="A596" s="1">
+        <v>46273</v>
+      </c>
+      <c r="B596">
+        <v>226.7</v>
+      </c>
+      <c r="C596">
+        <v>255.7</v>
+      </c>
+      <c r="D596">
+        <v>215.4</v>
+      </c>
+      <c r="E596">
+        <v>215.4</v>
+      </c>
+      <c r="F596">
+        <v>227.6</v>
+      </c>
+      <c r="G596">
+        <v>262.4</v>
+      </c>
+      <c r="H596">
+        <v>226.9</v>
+      </c>
+      <c r="I596">
+        <v>255.8</v>
+      </c>
+      <c r="J596">
+        <v>248.7</v>
+      </c>
+      <c r="K596">
+        <v>257.6</v>
+      </c>
+      <c r="L596">
+        <v>226.6</v>
+      </c>
+      <c r="M596">
+        <v>255.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M596"/>
+  <dimension ref="A1:M597"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24826,19 +24826,60 @@
         <v>226.9</v>
       </c>
       <c r="I596">
-        <v>255.8</v>
+        <v>259.6</v>
       </c>
       <c r="J596">
         <v>248.7</v>
       </c>
       <c r="K596">
-        <v>257.6</v>
+        <v>261.6</v>
       </c>
       <c r="L596">
         <v>226.6</v>
       </c>
       <c r="M596">
-        <v>255.7</v>
+        <v>259.5</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13">
+      <c r="A597" s="1">
+        <v>46274</v>
+      </c>
+      <c r="B597">
+        <v>229.7</v>
+      </c>
+      <c r="C597">
+        <v>258.7</v>
+      </c>
+      <c r="D597">
+        <v>215.4</v>
+      </c>
+      <c r="E597">
+        <v>215.4</v>
+      </c>
+      <c r="F597">
+        <v>229.6</v>
+      </c>
+      <c r="G597">
+        <v>262.4</v>
+      </c>
+      <c r="H597">
+        <v>230.7</v>
+      </c>
+      <c r="I597">
+        <v>259.6</v>
+      </c>
+      <c r="J597">
+        <v>252.7</v>
+      </c>
+      <c r="K597">
+        <v>261.6</v>
+      </c>
+      <c r="L597">
+        <v>226.6</v>
+      </c>
+      <c r="M597">
+        <v>259.5</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M597"/>
+  <dimension ref="A1:M596"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24720,7 +24720,7 @@
     </row>
     <row r="594" spans="1:13">
       <c r="A594" s="1">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="B594">
         <v>226.7</v>
@@ -24744,30 +24744,30 @@
         <v>226.9</v>
       </c>
       <c r="I594">
-        <v>255.8</v>
+        <v>259.6</v>
       </c>
       <c r="J594">
         <v>248.7</v>
       </c>
       <c r="K594">
-        <v>257.6</v>
+        <v>261.6</v>
       </c>
       <c r="L594">
         <v>226.6</v>
       </c>
       <c r="M594">
-        <v>255.7</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="595" spans="1:13">
       <c r="A595" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B595">
-        <v>226.7</v>
+        <v>229.7</v>
       </c>
       <c r="C595">
-        <v>255.7</v>
+        <v>258.7</v>
       </c>
       <c r="D595">
         <v>215.4</v>
@@ -24776,39 +24776,39 @@
         <v>215.4</v>
       </c>
       <c r="F595">
-        <v>227.6</v>
+        <v>229.6</v>
       </c>
       <c r="G595">
         <v>262.4</v>
       </c>
       <c r="H595">
-        <v>226.9</v>
+        <v>229.6</v>
       </c>
       <c r="I595">
-        <v>255.8</v>
+        <v>259.6</v>
       </c>
       <c r="J595">
-        <v>248.7</v>
+        <v>252.7</v>
       </c>
       <c r="K595">
-        <v>257.6</v>
+        <v>261.6</v>
       </c>
       <c r="L595">
         <v>226.6</v>
       </c>
       <c r="M595">
-        <v>255.7</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="596" spans="1:13">
       <c r="A596" s="1">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B596">
-        <v>226.7</v>
+        <v>229.7</v>
       </c>
       <c r="C596">
-        <v>255.7</v>
+        <v>258.7</v>
       </c>
       <c r="D596">
         <v>215.4</v>
@@ -24817,69 +24817,28 @@
         <v>215.4</v>
       </c>
       <c r="F596">
-        <v>227.6</v>
+        <v>229.6</v>
       </c>
       <c r="G596">
         <v>262.4</v>
       </c>
       <c r="H596">
-        <v>226.9</v>
+        <v>229.5</v>
       </c>
       <c r="I596">
-        <v>259.6</v>
+        <v>258.5</v>
       </c>
       <c r="J596">
-        <v>248.7</v>
+        <v>252.7</v>
       </c>
       <c r="K596">
         <v>261.6</v>
       </c>
       <c r="L596">
-        <v>226.6</v>
+        <v>229.5</v>
       </c>
       <c r="M596">
-        <v>259.5</v>
-      </c>
-    </row>
-    <row r="597" spans="1:13">
-      <c r="A597" s="1">
-        <v>46274</v>
-      </c>
-      <c r="B597">
-        <v>229.7</v>
-      </c>
-      <c r="C597">
-        <v>258.7</v>
-      </c>
-      <c r="D597">
-        <v>215.4</v>
-      </c>
-      <c r="E597">
-        <v>215.4</v>
-      </c>
-      <c r="F597">
-        <v>229.6</v>
-      </c>
-      <c r="G597">
-        <v>262.4</v>
-      </c>
-      <c r="H597">
-        <v>230.7</v>
-      </c>
-      <c r="I597">
-        <v>259.6</v>
-      </c>
-      <c r="J597">
-        <v>252.7</v>
-      </c>
-      <c r="K597">
-        <v>261.6</v>
-      </c>
-      <c r="L597">
-        <v>226.6</v>
-      </c>
-      <c r="M597">
-        <v>259.5</v>
+        <v>258.4</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M596"/>
+  <dimension ref="A1:M597"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24835,10 +24835,51 @@
         <v>261.6</v>
       </c>
       <c r="L596">
-        <v>229.5</v>
+        <v>229.4</v>
       </c>
       <c r="M596">
         <v>258.4</v>
+      </c>
+    </row>
+    <row r="597" spans="1:13">
+      <c r="A597" s="1">
+        <v>46276</v>
+      </c>
+      <c r="B597">
+        <v>229.7</v>
+      </c>
+      <c r="C597">
+        <v>258.7</v>
+      </c>
+      <c r="D597">
+        <v>215.4</v>
+      </c>
+      <c r="E597">
+        <v>215.4</v>
+      </c>
+      <c r="F597">
+        <v>229.6</v>
+      </c>
+      <c r="G597">
+        <v>265.4</v>
+      </c>
+      <c r="H597">
+        <v>229.5</v>
+      </c>
+      <c r="I597">
+        <v>261.5</v>
+      </c>
+      <c r="J597">
+        <v>252.7</v>
+      </c>
+      <c r="K597">
+        <v>264.6</v>
+      </c>
+      <c r="L597">
+        <v>229.4</v>
+      </c>
+      <c r="M597">
+        <v>261.4</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M597"/>
+  <dimension ref="A1:M598"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24849,7 +24849,7 @@
         <v>229.7</v>
       </c>
       <c r="C597">
-        <v>258.7</v>
+        <v>261.5</v>
       </c>
       <c r="D597">
         <v>215.4</v>
@@ -24879,6 +24879,47 @@
         <v>229.4</v>
       </c>
       <c r="M597">
+        <v>261.4</v>
+      </c>
+    </row>
+    <row r="598" spans="1:13">
+      <c r="A598" s="1">
+        <v>46277</v>
+      </c>
+      <c r="B598">
+        <v>229.7</v>
+      </c>
+      <c r="C598">
+        <v>261.5</v>
+      </c>
+      <c r="D598">
+        <v>215.4</v>
+      </c>
+      <c r="E598">
+        <v>215.4</v>
+      </c>
+      <c r="F598">
+        <v>229.6</v>
+      </c>
+      <c r="G598">
+        <v>265.4</v>
+      </c>
+      <c r="H598">
+        <v>229.5</v>
+      </c>
+      <c r="I598">
+        <v>261.5</v>
+      </c>
+      <c r="J598">
+        <v>252.7</v>
+      </c>
+      <c r="K598">
+        <v>264.6</v>
+      </c>
+      <c r="L598">
+        <v>229.4</v>
+      </c>
+      <c r="M598">
         <v>261.4</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M598"/>
+  <dimension ref="A1:M599"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24923,6 +24923,47 @@
         <v>261.4</v>
       </c>
     </row>
+    <row r="599" spans="1:13">
+      <c r="A599" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B599">
+        <v>229.7</v>
+      </c>
+      <c r="C599">
+        <v>261.5</v>
+      </c>
+      <c r="D599">
+        <v>215.4</v>
+      </c>
+      <c r="E599">
+        <v>215.4</v>
+      </c>
+      <c r="F599">
+        <v>229.6</v>
+      </c>
+      <c r="G599">
+        <v>265.4</v>
+      </c>
+      <c r="H599">
+        <v>229.5</v>
+      </c>
+      <c r="I599">
+        <v>261.5</v>
+      </c>
+      <c r="J599">
+        <v>252.7</v>
+      </c>
+      <c r="K599">
+        <v>264.6</v>
+      </c>
+      <c r="L599">
+        <v>229.4</v>
+      </c>
+      <c r="M599">
+        <v>261.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M599"/>
+  <dimension ref="A1:M600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24964,6 +24964,47 @@
         <v>261.4</v>
       </c>
     </row>
+    <row r="600" spans="1:13">
+      <c r="A600" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B600">
+        <v>232.4</v>
+      </c>
+      <c r="C600">
+        <v>261.4</v>
+      </c>
+      <c r="D600">
+        <v>215.4</v>
+      </c>
+      <c r="E600">
+        <v>215.4</v>
+      </c>
+      <c r="F600">
+        <v>232.6</v>
+      </c>
+      <c r="G600">
+        <v>265.4</v>
+      </c>
+      <c r="H600">
+        <v>232.5</v>
+      </c>
+      <c r="I600">
+        <v>261.5</v>
+      </c>
+      <c r="J600">
+        <v>255.7</v>
+      </c>
+      <c r="K600">
+        <v>264.6</v>
+      </c>
+      <c r="L600">
+        <v>232.3</v>
+      </c>
+      <c r="M600">
+        <v>261.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M600"/>
+  <dimension ref="A1:M601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25005,6 +25005,47 @@
         <v>261.4</v>
       </c>
     </row>
+    <row r="601" spans="1:13">
+      <c r="A601" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B601">
+        <v>232.4</v>
+      </c>
+      <c r="C601">
+        <v>261.4</v>
+      </c>
+      <c r="D601">
+        <v>215.4</v>
+      </c>
+      <c r="E601">
+        <v>215.4</v>
+      </c>
+      <c r="F601">
+        <v>235.6</v>
+      </c>
+      <c r="G601">
+        <v>268.4</v>
+      </c>
+      <c r="H601">
+        <v>232.5</v>
+      </c>
+      <c r="I601">
+        <v>261.5</v>
+      </c>
+      <c r="J601">
+        <v>255.7</v>
+      </c>
+      <c r="K601">
+        <v>264.6</v>
+      </c>
+      <c r="L601">
+        <v>232.3</v>
+      </c>
+      <c r="M601">
+        <v>261.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M601"/>
+  <dimension ref="A1:M600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -24884,13 +24884,13 @@
     </row>
     <row r="598" spans="1:13">
       <c r="A598" s="1">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B598">
-        <v>229.7</v>
+        <v>232.4</v>
       </c>
       <c r="C598">
-        <v>261.5</v>
+        <v>261.4</v>
       </c>
       <c r="D598">
         <v>215.4</v>
@@ -24899,25 +24899,25 @@
         <v>215.4</v>
       </c>
       <c r="F598">
-        <v>229.6</v>
+        <v>232.6</v>
       </c>
       <c r="G598">
         <v>265.4</v>
       </c>
       <c r="H598">
-        <v>229.5</v>
+        <v>232.5</v>
       </c>
       <c r="I598">
         <v>261.5</v>
       </c>
       <c r="J598">
-        <v>252.7</v>
+        <v>255.7</v>
       </c>
       <c r="K598">
         <v>264.6</v>
       </c>
       <c r="L598">
-        <v>229.4</v>
+        <v>232.3</v>
       </c>
       <c r="M598">
         <v>261.4</v>
@@ -24925,13 +24925,13 @@
     </row>
     <row r="599" spans="1:13">
       <c r="A599" s="1">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="B599">
-        <v>229.7</v>
+        <v>232.4</v>
       </c>
       <c r="C599">
-        <v>261.5</v>
+        <v>261.4</v>
       </c>
       <c r="D599">
         <v>215.4</v>
@@ -24940,25 +24940,25 @@
         <v>215.4</v>
       </c>
       <c r="F599">
-        <v>229.6</v>
+        <v>235.6</v>
       </c>
       <c r="G599">
-        <v>265.4</v>
+        <v>268.4</v>
       </c>
       <c r="H599">
-        <v>229.5</v>
+        <v>232.5</v>
       </c>
       <c r="I599">
         <v>261.5</v>
       </c>
       <c r="J599">
-        <v>252.7</v>
+        <v>255.7</v>
       </c>
       <c r="K599">
         <v>264.6</v>
       </c>
       <c r="L599">
-        <v>229.4</v>
+        <v>232.3</v>
       </c>
       <c r="M599">
         <v>261.4</v>
@@ -24966,13 +24966,13 @@
     </row>
     <row r="600" spans="1:13">
       <c r="A600" s="1">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="B600">
         <v>232.4</v>
       </c>
       <c r="C600">
-        <v>261.4</v>
+        <v>264.4</v>
       </c>
       <c r="D600">
         <v>215.4</v>
@@ -24981,69 +24981,28 @@
         <v>215.4</v>
       </c>
       <c r="F600">
-        <v>232.6</v>
+        <v>235.6</v>
       </c>
       <c r="G600">
-        <v>265.4</v>
+        <v>270.4</v>
       </c>
       <c r="H600">
         <v>232.5</v>
       </c>
       <c r="I600">
-        <v>261.5</v>
+        <v>264.5</v>
       </c>
       <c r="J600">
         <v>255.7</v>
       </c>
       <c r="K600">
-        <v>264.6</v>
+        <v>267.6</v>
       </c>
       <c r="L600">
         <v>232.3</v>
       </c>
       <c r="M600">
-        <v>261.4</v>
-      </c>
-    </row>
-    <row r="601" spans="1:13">
-      <c r="A601" s="1">
-        <v>46280</v>
-      </c>
-      <c r="B601">
-        <v>232.4</v>
-      </c>
-      <c r="C601">
-        <v>261.4</v>
-      </c>
-      <c r="D601">
-        <v>215.4</v>
-      </c>
-      <c r="E601">
-        <v>215.4</v>
-      </c>
-      <c r="F601">
-        <v>235.6</v>
-      </c>
-      <c r="G601">
-        <v>268.4</v>
-      </c>
-      <c r="H601">
-        <v>232.5</v>
-      </c>
-      <c r="I601">
-        <v>261.5</v>
-      </c>
-      <c r="J601">
-        <v>255.7</v>
-      </c>
-      <c r="K601">
-        <v>264.6</v>
-      </c>
-      <c r="L601">
-        <v>232.3</v>
-      </c>
-      <c r="M601">
-        <v>261.4</v>
+        <v>264.4</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M600"/>
+  <dimension ref="A1:M601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25005,6 +25005,47 @@
         <v>264.4</v>
       </c>
     </row>
+    <row r="601" spans="1:13">
+      <c r="A601" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B601">
+        <v>235.4</v>
+      </c>
+      <c r="C601">
+        <v>268.4</v>
+      </c>
+      <c r="D601">
+        <v>222.3</v>
+      </c>
+      <c r="E601">
+        <v>222.3</v>
+      </c>
+      <c r="F601">
+        <v>239.6</v>
+      </c>
+      <c r="G601">
+        <v>272.4</v>
+      </c>
+      <c r="H601">
+        <v>235.5</v>
+      </c>
+      <c r="I601">
+        <v>268.5</v>
+      </c>
+      <c r="J601">
+        <v>258.7</v>
+      </c>
+      <c r="K601">
+        <v>271.6</v>
+      </c>
+      <c r="L601">
+        <v>235.3</v>
+      </c>
+      <c r="M601">
+        <v>268.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M601"/>
+  <dimension ref="A1:M602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25046,6 +25046,47 @@
         <v>268.4</v>
       </c>
     </row>
+    <row r="602" spans="1:13">
+      <c r="A602" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B602">
+        <v>239.4</v>
+      </c>
+      <c r="C602">
+        <v>268.4</v>
+      </c>
+      <c r="D602">
+        <v>222.3</v>
+      </c>
+      <c r="E602">
+        <v>222.3</v>
+      </c>
+      <c r="F602">
+        <v>242.6</v>
+      </c>
+      <c r="G602">
+        <v>275.4</v>
+      </c>
+      <c r="H602">
+        <v>239.5</v>
+      </c>
+      <c r="I602">
+        <v>268.5</v>
+      </c>
+      <c r="J602">
+        <v>262.7</v>
+      </c>
+      <c r="K602">
+        <v>271.6</v>
+      </c>
+      <c r="L602">
+        <v>239.3</v>
+      </c>
+      <c r="M602">
+        <v>268.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M602"/>
+  <dimension ref="A1:M603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25054,7 +25054,7 @@
         <v>239.4</v>
       </c>
       <c r="C602">
-        <v>268.4</v>
+        <v>271.4</v>
       </c>
       <c r="D602">
         <v>222.3</v>
@@ -25084,6 +25084,47 @@
         <v>239.3</v>
       </c>
       <c r="M602">
+        <v>268.4</v>
+      </c>
+    </row>
+    <row r="603" spans="1:13">
+      <c r="A603" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B603">
+        <v>239.4</v>
+      </c>
+      <c r="C603">
+        <v>271.4</v>
+      </c>
+      <c r="D603">
+        <v>222.3</v>
+      </c>
+      <c r="E603">
+        <v>222.3</v>
+      </c>
+      <c r="F603">
+        <v>242.6</v>
+      </c>
+      <c r="G603">
+        <v>275.4</v>
+      </c>
+      <c r="H603">
+        <v>239.5</v>
+      </c>
+      <c r="I603">
+        <v>268.5</v>
+      </c>
+      <c r="J603">
+        <v>262.7</v>
+      </c>
+      <c r="K603">
+        <v>271.6</v>
+      </c>
+      <c r="L603">
+        <v>239.3</v>
+      </c>
+      <c r="M603">
         <v>268.4</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M603"/>
+  <dimension ref="A1:M604"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25128,6 +25128,47 @@
         <v>268.4</v>
       </c>
     </row>
+    <row r="604" spans="1:13">
+      <c r="A604" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B604">
+        <v>239.4</v>
+      </c>
+      <c r="C604">
+        <v>271.4</v>
+      </c>
+      <c r="D604">
+        <v>222.3</v>
+      </c>
+      <c r="E604">
+        <v>222.3</v>
+      </c>
+      <c r="F604">
+        <v>242.6</v>
+      </c>
+      <c r="G604">
+        <v>275.4</v>
+      </c>
+      <c r="H604">
+        <v>239.5</v>
+      </c>
+      <c r="I604">
+        <v>268.5</v>
+      </c>
+      <c r="J604">
+        <v>262.7</v>
+      </c>
+      <c r="K604">
+        <v>271.6</v>
+      </c>
+      <c r="L604">
+        <v>239.3</v>
+      </c>
+      <c r="M604">
+        <v>268.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M604"/>
+  <dimension ref="A1:M605"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25133,16 +25133,16 @@
         <v>46285</v>
       </c>
       <c r="B604">
-        <v>239.4</v>
+        <v>242.4</v>
       </c>
       <c r="C604">
         <v>271.4</v>
       </c>
       <c r="D604">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="E604">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="F604">
         <v>242.6</v>
@@ -25151,7 +25151,7 @@
         <v>275.4</v>
       </c>
       <c r="H604">
-        <v>239.5</v>
+        <v>242.5</v>
       </c>
       <c r="I604">
         <v>268.5</v>
@@ -25163,10 +25163,51 @@
         <v>271.6</v>
       </c>
       <c r="L604">
-        <v>239.3</v>
+        <v>242.3</v>
       </c>
       <c r="M604">
         <v>268.4</v>
+      </c>
+    </row>
+    <row r="605" spans="1:13">
+      <c r="A605" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B605">
+        <v>242.4</v>
+      </c>
+      <c r="C605">
+        <v>273.4</v>
+      </c>
+      <c r="D605">
+        <v>232.3</v>
+      </c>
+      <c r="E605">
+        <v>232.3</v>
+      </c>
+      <c r="F605">
+        <v>242.6</v>
+      </c>
+      <c r="G605">
+        <v>277.4</v>
+      </c>
+      <c r="H605">
+        <v>242.5</v>
+      </c>
+      <c r="I605">
+        <v>273.5</v>
+      </c>
+      <c r="J605">
+        <v>262.7</v>
+      </c>
+      <c r="K605">
+        <v>276.6</v>
+      </c>
+      <c r="L605">
+        <v>242.3</v>
+      </c>
+      <c r="M605">
+        <v>273.4</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M605"/>
+  <dimension ref="A1:M606"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25210,6 +25210,47 @@
         <v>273.4</v>
       </c>
     </row>
+    <row r="606" spans="1:13">
+      <c r="A606" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B606">
+        <v>244.4</v>
+      </c>
+      <c r="C606">
+        <v>273.4</v>
+      </c>
+      <c r="D606">
+        <v>232.3</v>
+      </c>
+      <c r="E606">
+        <v>232.3</v>
+      </c>
+      <c r="F606">
+        <v>246.6</v>
+      </c>
+      <c r="G606">
+        <v>279.4</v>
+      </c>
+      <c r="H606">
+        <v>244.5</v>
+      </c>
+      <c r="I606">
+        <v>273.5</v>
+      </c>
+      <c r="J606">
+        <v>267.7</v>
+      </c>
+      <c r="K606">
+        <v>276.6</v>
+      </c>
+      <c r="L606">
+        <v>244.3</v>
+      </c>
+      <c r="M606">
+        <v>273.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25089,19 +25089,19 @@
     </row>
     <row r="603" spans="1:13">
       <c r="A603" s="1">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B603">
-        <v>239.4</v>
+        <v>242.4</v>
       </c>
       <c r="C603">
         <v>271.4</v>
       </c>
       <c r="D603">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="E603">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="F603">
         <v>242.6</v>
@@ -25110,7 +25110,7 @@
         <v>275.4</v>
       </c>
       <c r="H603">
-        <v>239.5</v>
+        <v>242.5</v>
       </c>
       <c r="I603">
         <v>268.5</v>
@@ -25122,7 +25122,7 @@
         <v>271.6</v>
       </c>
       <c r="L603">
-        <v>239.3</v>
+        <v>242.3</v>
       </c>
       <c r="M603">
         <v>268.4</v>
@@ -25130,13 +25130,13 @@
     </row>
     <row r="604" spans="1:13">
       <c r="A604" s="1">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B604">
         <v>242.4</v>
       </c>
       <c r="C604">
-        <v>271.4</v>
+        <v>273.4</v>
       </c>
       <c r="D604">
         <v>232.3</v>
@@ -25148,33 +25148,33 @@
         <v>242.6</v>
       </c>
       <c r="G604">
-        <v>275.4</v>
+        <v>277.4</v>
       </c>
       <c r="H604">
         <v>242.5</v>
       </c>
       <c r="I604">
-        <v>268.5</v>
+        <v>273.5</v>
       </c>
       <c r="J604">
         <v>262.7</v>
       </c>
       <c r="K604">
-        <v>271.6</v>
+        <v>276.6</v>
       </c>
       <c r="L604">
         <v>242.3</v>
       </c>
       <c r="M604">
-        <v>268.4</v>
+        <v>273.4</v>
       </c>
     </row>
     <row r="605" spans="1:13">
       <c r="A605" s="1">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B605">
-        <v>242.4</v>
+        <v>244.4</v>
       </c>
       <c r="C605">
         <v>273.4</v>
@@ -25186,25 +25186,25 @@
         <v>232.3</v>
       </c>
       <c r="F605">
-        <v>242.6</v>
+        <v>246.6</v>
       </c>
       <c r="G605">
-        <v>277.4</v>
+        <v>279.4</v>
       </c>
       <c r="H605">
-        <v>242.5</v>
+        <v>244.5</v>
       </c>
       <c r="I605">
         <v>273.5</v>
       </c>
       <c r="J605">
-        <v>262.7</v>
+        <v>267.7</v>
       </c>
       <c r="K605">
         <v>276.6</v>
       </c>
       <c r="L605">
-        <v>242.3</v>
+        <v>244.3</v>
       </c>
       <c r="M605">
         <v>273.4</v>
@@ -25212,7 +25212,7 @@
     </row>
     <row r="606" spans="1:13">
       <c r="A606" s="1">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B606">
         <v>244.4</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M606"/>
+  <dimension ref="A1:M607"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25251,6 +25251,47 @@
         <v>273.4</v>
       </c>
     </row>
+    <row r="607" spans="1:13">
+      <c r="A607" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B607">
+        <v>244.4</v>
+      </c>
+      <c r="C607">
+        <v>273.4</v>
+      </c>
+      <c r="D607">
+        <v>232.3</v>
+      </c>
+      <c r="E607">
+        <v>232.3</v>
+      </c>
+      <c r="F607">
+        <v>249.6</v>
+      </c>
+      <c r="G607">
+        <v>282.4</v>
+      </c>
+      <c r="H607">
+        <v>244.5</v>
+      </c>
+      <c r="I607">
+        <v>273.5</v>
+      </c>
+      <c r="J607">
+        <v>267.7</v>
+      </c>
+      <c r="K607">
+        <v>276.6</v>
+      </c>
+      <c r="L607">
+        <v>244.3</v>
+      </c>
+      <c r="M607">
+        <v>273.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M607"/>
+  <dimension ref="A1:M608"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25259,7 +25259,7 @@
         <v>244.4</v>
       </c>
       <c r="C607">
-        <v>273.4</v>
+        <v>278.4</v>
       </c>
       <c r="D607">
         <v>232.3</v>
@@ -25277,19 +25277,60 @@
         <v>244.5</v>
       </c>
       <c r="I607">
-        <v>273.5</v>
+        <v>278.5</v>
       </c>
       <c r="J607">
         <v>267.7</v>
       </c>
       <c r="K607">
-        <v>276.6</v>
+        <v>281.6</v>
       </c>
       <c r="L607">
         <v>244.3</v>
       </c>
       <c r="M607">
-        <v>273.4</v>
+        <v>278.4</v>
+      </c>
+    </row>
+    <row r="608" spans="1:13">
+      <c r="A608" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B608">
+        <v>249.4</v>
+      </c>
+      <c r="C608">
+        <v>278.4</v>
+      </c>
+      <c r="D608">
+        <v>232.3</v>
+      </c>
+      <c r="E608">
+        <v>232.3</v>
+      </c>
+      <c r="F608">
+        <v>251.6</v>
+      </c>
+      <c r="G608">
+        <v>284.4</v>
+      </c>
+      <c r="H608">
+        <v>249.5</v>
+      </c>
+      <c r="I608">
+        <v>278.5</v>
+      </c>
+      <c r="J608">
+        <v>272.7</v>
+      </c>
+      <c r="K608">
+        <v>281.6</v>
+      </c>
+      <c r="L608">
+        <v>249.3</v>
+      </c>
+      <c r="M608">
+        <v>278.4</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M608"/>
+  <dimension ref="A1:M609"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25333,6 +25333,47 @@
         <v>278.4</v>
       </c>
     </row>
+    <row r="609" spans="1:13">
+      <c r="A609" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B609">
+        <v>249.4</v>
+      </c>
+      <c r="C609">
+        <v>278.4</v>
+      </c>
+      <c r="D609">
+        <v>232.3</v>
+      </c>
+      <c r="E609">
+        <v>232.3</v>
+      </c>
+      <c r="F609">
+        <v>251.6</v>
+      </c>
+      <c r="G609">
+        <v>284.4</v>
+      </c>
+      <c r="H609">
+        <v>249.5</v>
+      </c>
+      <c r="I609">
+        <v>278.5</v>
+      </c>
+      <c r="J609">
+        <v>272.7</v>
+      </c>
+      <c r="K609">
+        <v>281.6</v>
+      </c>
+      <c r="L609">
+        <v>249.3</v>
+      </c>
+      <c r="M609">
+        <v>278.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25212,13 +25212,13 @@
     </row>
     <row r="606" spans="1:13">
       <c r="A606" s="1">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B606">
         <v>244.4</v>
       </c>
       <c r="C606">
-        <v>273.4</v>
+        <v>278.4</v>
       </c>
       <c r="D606">
         <v>232.3</v>
@@ -25227,36 +25227,36 @@
         <v>232.3</v>
       </c>
       <c r="F606">
-        <v>246.6</v>
+        <v>249.6</v>
       </c>
       <c r="G606">
-        <v>279.4</v>
+        <v>282.4</v>
       </c>
       <c r="H606">
         <v>244.5</v>
       </c>
       <c r="I606">
-        <v>273.5</v>
+        <v>278.5</v>
       </c>
       <c r="J606">
         <v>267.7</v>
       </c>
       <c r="K606">
-        <v>276.6</v>
+        <v>281.6</v>
       </c>
       <c r="L606">
         <v>244.3</v>
       </c>
       <c r="M606">
-        <v>273.4</v>
+        <v>278.4</v>
       </c>
     </row>
     <row r="607" spans="1:13">
       <c r="A607" s="1">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B607">
-        <v>244.4</v>
+        <v>249.4</v>
       </c>
       <c r="C607">
         <v>278.4</v>
@@ -25268,25 +25268,25 @@
         <v>232.3</v>
       </c>
       <c r="F607">
-        <v>249.6</v>
+        <v>251.6</v>
       </c>
       <c r="G607">
-        <v>282.4</v>
+        <v>284.4</v>
       </c>
       <c r="H607">
-        <v>244.5</v>
+        <v>249.5</v>
       </c>
       <c r="I607">
         <v>278.5</v>
       </c>
       <c r="J607">
-        <v>267.7</v>
+        <v>272.7</v>
       </c>
       <c r="K607">
         <v>281.6</v>
       </c>
       <c r="L607">
-        <v>244.3</v>
+        <v>249.3</v>
       </c>
       <c r="M607">
         <v>278.4</v>
@@ -25294,7 +25294,7 @@
     </row>
     <row r="608" spans="1:13">
       <c r="A608" s="1">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B608">
         <v>249.4</v>
@@ -25303,10 +25303,10 @@
         <v>278.4</v>
       </c>
       <c r="D608">
-        <v>232.3</v>
+        <v>239.3</v>
       </c>
       <c r="E608">
-        <v>232.3</v>
+        <v>239.3</v>
       </c>
       <c r="F608">
         <v>251.6</v>
@@ -25335,7 +25335,7 @@
     </row>
     <row r="609" spans="1:13">
       <c r="A609" s="1">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B609">
         <v>249.4</v>
@@ -25344,10 +25344,10 @@
         <v>278.4</v>
       </c>
       <c r="D609">
-        <v>232.3</v>
+        <v>239.3</v>
       </c>
       <c r="E609">
-        <v>232.3</v>
+        <v>239.3</v>
       </c>
       <c r="F609">
         <v>251.6</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M609"/>
+  <dimension ref="A1:M610"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25374,6 +25374,47 @@
         <v>278.4</v>
       </c>
     </row>
+    <row r="610" spans="1:13">
+      <c r="A610" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B610">
+        <v>249.4</v>
+      </c>
+      <c r="C610">
+        <v>278.4</v>
+      </c>
+      <c r="D610">
+        <v>239.3</v>
+      </c>
+      <c r="E610">
+        <v>239.3</v>
+      </c>
+      <c r="F610">
+        <v>251.6</v>
+      </c>
+      <c r="G610">
+        <v>284.4</v>
+      </c>
+      <c r="H610">
+        <v>249.5</v>
+      </c>
+      <c r="I610">
+        <v>280.5</v>
+      </c>
+      <c r="J610">
+        <v>272.7</v>
+      </c>
+      <c r="K610">
+        <v>281.6</v>
+      </c>
+      <c r="L610">
+        <v>249.3</v>
+      </c>
+      <c r="M610">
+        <v>280.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M610"/>
+  <dimension ref="A1:M611"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25415,6 +25415,47 @@
         <v>280.4</v>
       </c>
     </row>
+    <row r="611" spans="1:13">
+      <c r="A611" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B611">
+        <v>251.4</v>
+      </c>
+      <c r="C611">
+        <v>280.4</v>
+      </c>
+      <c r="D611">
+        <v>239.3</v>
+      </c>
+      <c r="E611">
+        <v>239.3</v>
+      </c>
+      <c r="F611">
+        <v>251.6</v>
+      </c>
+      <c r="G611">
+        <v>284.4</v>
+      </c>
+      <c r="H611">
+        <v>251.5</v>
+      </c>
+      <c r="I611">
+        <v>280.5</v>
+      </c>
+      <c r="J611">
+        <v>272.7</v>
+      </c>
+      <c r="K611">
+        <v>281.6</v>
+      </c>
+      <c r="L611">
+        <v>249.3</v>
+      </c>
+      <c r="M611">
+        <v>280.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M611"/>
+  <dimension ref="A1:M612"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25456,6 +25456,47 @@
         <v>280.4</v>
       </c>
     </row>
+    <row r="612" spans="1:13">
+      <c r="A612" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B612">
+        <v>251.4</v>
+      </c>
+      <c r="C612">
+        <v>280.4</v>
+      </c>
+      <c r="D612">
+        <v>239.3</v>
+      </c>
+      <c r="E612">
+        <v>239.3</v>
+      </c>
+      <c r="F612">
+        <v>251.6</v>
+      </c>
+      <c r="G612">
+        <v>284.4</v>
+      </c>
+      <c r="H612">
+        <v>251.5</v>
+      </c>
+      <c r="I612">
+        <v>281.4</v>
+      </c>
+      <c r="J612">
+        <v>272.7</v>
+      </c>
+      <c r="K612">
+        <v>283.6</v>
+      </c>
+      <c r="L612">
+        <v>251.3</v>
+      </c>
+      <c r="M612">
+        <v>281.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25335,7 +25335,7 @@
     </row>
     <row r="609" spans="1:13">
       <c r="A609" s="1">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B609">
         <v>249.4</v>
@@ -25359,7 +25359,7 @@
         <v>249.5</v>
       </c>
       <c r="I609">
-        <v>278.5</v>
+        <v>280.5</v>
       </c>
       <c r="J609">
         <v>272.7</v>
@@ -25371,18 +25371,18 @@
         <v>249.3</v>
       </c>
       <c r="M609">
-        <v>278.4</v>
+        <v>280.4</v>
       </c>
     </row>
     <row r="610" spans="1:13">
       <c r="A610" s="1">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B610">
-        <v>249.4</v>
+        <v>251.4</v>
       </c>
       <c r="C610">
-        <v>278.4</v>
+        <v>280.4</v>
       </c>
       <c r="D610">
         <v>239.3</v>
@@ -25397,7 +25397,7 @@
         <v>284.4</v>
       </c>
       <c r="H610">
-        <v>249.5</v>
+        <v>251.5</v>
       </c>
       <c r="I610">
         <v>280.5</v>
@@ -25417,7 +25417,7 @@
     </row>
     <row r="611" spans="1:13">
       <c r="A611" s="1">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B611">
         <v>251.4</v>
@@ -25441,24 +25441,24 @@
         <v>251.5</v>
       </c>
       <c r="I611">
-        <v>280.5</v>
+        <v>281.4</v>
       </c>
       <c r="J611">
         <v>272.7</v>
       </c>
       <c r="K611">
-        <v>281.6</v>
+        <v>283.6</v>
       </c>
       <c r="L611">
-        <v>249.3</v>
+        <v>251.3</v>
       </c>
       <c r="M611">
-        <v>280.4</v>
+        <v>281.3</v>
       </c>
     </row>
     <row r="612" spans="1:13">
       <c r="A612" s="1">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B612">
         <v>251.4</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M612"/>
+  <dimension ref="A1:M613"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25497,6 +25497,47 @@
         <v>281.3</v>
       </c>
     </row>
+    <row r="613" spans="1:13">
+      <c r="A613" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B613">
+        <v>251.4</v>
+      </c>
+      <c r="C613">
+        <v>281.3</v>
+      </c>
+      <c r="D613">
+        <v>239.3</v>
+      </c>
+      <c r="E613">
+        <v>239.3</v>
+      </c>
+      <c r="F613">
+        <v>253.6</v>
+      </c>
+      <c r="G613">
+        <v>286.4</v>
+      </c>
+      <c r="H613">
+        <v>252.4</v>
+      </c>
+      <c r="I613">
+        <v>282.4</v>
+      </c>
+      <c r="J613">
+        <v>274.7</v>
+      </c>
+      <c r="K613">
+        <v>285.6</v>
+      </c>
+      <c r="L613">
+        <v>251.3</v>
+      </c>
+      <c r="M613">
+        <v>281.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M613"/>
+  <dimension ref="A1:M614"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25505,7 +25505,7 @@
         <v>251.4</v>
       </c>
       <c r="C613">
-        <v>281.3</v>
+        <v>282.3</v>
       </c>
       <c r="D613">
         <v>239.3</v>
@@ -25535,7 +25535,48 @@
         <v>251.3</v>
       </c>
       <c r="M613">
-        <v>281.3</v>
+        <v>282.3</v>
+      </c>
+    </row>
+    <row r="614" spans="1:13">
+      <c r="A614" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B614">
+        <v>251.4</v>
+      </c>
+      <c r="C614">
+        <v>282.3</v>
+      </c>
+      <c r="D614">
+        <v>239.3</v>
+      </c>
+      <c r="E614">
+        <v>239.3</v>
+      </c>
+      <c r="F614">
+        <v>253.6</v>
+      </c>
+      <c r="G614">
+        <v>286.4</v>
+      </c>
+      <c r="H614">
+        <v>252.4</v>
+      </c>
+      <c r="I614">
+        <v>282.4</v>
+      </c>
+      <c r="J614">
+        <v>274.7</v>
+      </c>
+      <c r="K614">
+        <v>285.6</v>
+      </c>
+      <c r="L614">
+        <v>251.3</v>
+      </c>
+      <c r="M614">
+        <v>282.3</v>
       </c>
     </row>
   </sheetData>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M614"/>
+  <dimension ref="A1:M615"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25579,6 +25579,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="615" spans="1:13">
+      <c r="A615" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B615">
+        <v>251.4</v>
+      </c>
+      <c r="C615">
+        <v>282.3</v>
+      </c>
+      <c r="D615">
+        <v>239.3</v>
+      </c>
+      <c r="E615">
+        <v>239.3</v>
+      </c>
+      <c r="F615">
+        <v>253.6</v>
+      </c>
+      <c r="G615">
+        <v>286.4</v>
+      </c>
+      <c r="H615">
+        <v>252.4</v>
+      </c>
+      <c r="I615">
+        <v>282.4</v>
+      </c>
+      <c r="J615">
+        <v>274.7</v>
+      </c>
+      <c r="K615">
+        <v>285.6</v>
+      </c>
+      <c r="L615">
+        <v>251.3</v>
+      </c>
+      <c r="M615">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25458,13 +25458,13 @@
     </row>
     <row r="612" spans="1:13">
       <c r="A612" s="1">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B612">
         <v>251.4</v>
       </c>
       <c r="C612">
-        <v>280.4</v>
+        <v>282.3</v>
       </c>
       <c r="D612">
         <v>239.3</v>
@@ -25473,33 +25473,33 @@
         <v>239.3</v>
       </c>
       <c r="F612">
-        <v>251.6</v>
+        <v>253.6</v>
       </c>
       <c r="G612">
-        <v>284.4</v>
+        <v>286.4</v>
       </c>
       <c r="H612">
-        <v>251.5</v>
+        <v>252.4</v>
       </c>
       <c r="I612">
-        <v>281.4</v>
+        <v>282.4</v>
       </c>
       <c r="J612">
-        <v>272.7</v>
+        <v>274.7</v>
       </c>
       <c r="K612">
-        <v>283.6</v>
+        <v>285.6</v>
       </c>
       <c r="L612">
         <v>251.3</v>
       </c>
       <c r="M612">
-        <v>281.3</v>
+        <v>282.3</v>
       </c>
     </row>
     <row r="613" spans="1:13">
       <c r="A613" s="1">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B613">
         <v>251.4</v>
@@ -25540,19 +25540,19 @@
     </row>
     <row r="614" spans="1:13">
       <c r="A614" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B614">
-        <v>251.4</v>
+        <v>253.3</v>
       </c>
       <c r="C614">
         <v>282.3</v>
       </c>
       <c r="D614">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="E614">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="F614">
         <v>253.6</v>
@@ -25561,19 +25561,19 @@
         <v>286.4</v>
       </c>
       <c r="H614">
-        <v>252.4</v>
+        <v>253.4</v>
       </c>
       <c r="I614">
         <v>282.4</v>
       </c>
       <c r="J614">
-        <v>274.7</v>
+        <v>276.7</v>
       </c>
       <c r="K614">
         <v>285.6</v>
       </c>
       <c r="L614">
-        <v>251.3</v>
+        <v>253.2</v>
       </c>
       <c r="M614">
         <v>282.3</v>
@@ -25581,19 +25581,19 @@
     </row>
     <row r="615" spans="1:13">
       <c r="A615" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B615">
-        <v>251.4</v>
+        <v>253.3</v>
       </c>
       <c r="C615">
         <v>282.3</v>
       </c>
       <c r="D615">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="E615">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="F615">
         <v>253.6</v>
@@ -25602,19 +25602,19 @@
         <v>286.4</v>
       </c>
       <c r="H615">
-        <v>252.4</v>
+        <v>253.4</v>
       </c>
       <c r="I615">
         <v>282.4</v>
       </c>
       <c r="J615">
-        <v>274.7</v>
+        <v>276.7</v>
       </c>
       <c r="K615">
         <v>285.6</v>
       </c>
       <c r="L615">
-        <v>251.3</v>
+        <v>253.2</v>
       </c>
       <c r="M615">
         <v>282.3</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M615"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25620,6 +25620,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="616" spans="1:13">
+      <c r="A616" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B616">
+        <v>253.3</v>
+      </c>
+      <c r="C616">
+        <v>282.3</v>
+      </c>
+      <c r="D616">
+        <v>243.2</v>
+      </c>
+      <c r="E616">
+        <v>243.2</v>
+      </c>
+      <c r="F616">
+        <v>253.6</v>
+      </c>
+      <c r="G616">
+        <v>286.4</v>
+      </c>
+      <c r="H616">
+        <v>253.4</v>
+      </c>
+      <c r="I616">
+        <v>282.4</v>
+      </c>
+      <c r="J616">
+        <v>276.7</v>
+      </c>
+      <c r="K616">
+        <v>285.6</v>
+      </c>
+      <c r="L616">
+        <v>253.2</v>
+      </c>
+      <c r="M616">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25499,19 +25499,19 @@
     </row>
     <row r="613" spans="1:13">
       <c r="A613" s="1">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B613">
-        <v>251.4</v>
+        <v>253.3</v>
       </c>
       <c r="C613">
         <v>282.3</v>
       </c>
       <c r="D613">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="E613">
-        <v>239.3</v>
+        <v>243.2</v>
       </c>
       <c r="F613">
         <v>253.6</v>
@@ -25520,19 +25520,19 @@
         <v>286.4</v>
       </c>
       <c r="H613">
-        <v>252.4</v>
+        <v>253.4</v>
       </c>
       <c r="I613">
         <v>282.4</v>
       </c>
       <c r="J613">
-        <v>274.7</v>
+        <v>276.7</v>
       </c>
       <c r="K613">
         <v>285.6</v>
       </c>
       <c r="L613">
-        <v>251.3</v>
+        <v>253.2</v>
       </c>
       <c r="M613">
         <v>282.3</v>
@@ -25540,7 +25540,7 @@
     </row>
     <row r="614" spans="1:13">
       <c r="A614" s="1">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B614">
         <v>253.3</v>
@@ -25581,7 +25581,7 @@
     </row>
     <row r="615" spans="1:13">
       <c r="A615" s="1">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B615">
         <v>253.3</v>
@@ -25622,7 +25622,7 @@
     </row>
     <row r="616" spans="1:13">
       <c r="A616" s="1">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B616">
         <v>253.3</v>
@@ -25640,7 +25640,7 @@
         <v>253.6</v>
       </c>
       <c r="G616">
-        <v>286.4</v>
+        <v>287.4</v>
       </c>
       <c r="H616">
         <v>253.4</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M616"/>
+  <dimension ref="A1:M617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25661,6 +25661,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="617" spans="1:13">
+      <c r="A617" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B617">
+        <v>253.3</v>
+      </c>
+      <c r="C617">
+        <v>282.3</v>
+      </c>
+      <c r="D617">
+        <v>243.2</v>
+      </c>
+      <c r="E617">
+        <v>243.2</v>
+      </c>
+      <c r="F617">
+        <v>253.6</v>
+      </c>
+      <c r="G617">
+        <v>287.4</v>
+      </c>
+      <c r="H617">
+        <v>253.4</v>
+      </c>
+      <c r="I617">
+        <v>282.4</v>
+      </c>
+      <c r="J617">
+        <v>276.7</v>
+      </c>
+      <c r="K617">
+        <v>285.6</v>
+      </c>
+      <c r="L617">
+        <v>253.2</v>
+      </c>
+      <c r="M617">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M617"/>
+  <dimension ref="A1:M616"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25540,7 +25540,7 @@
     </row>
     <row r="614" spans="1:13">
       <c r="A614" s="1">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="B614">
         <v>253.3</v>
@@ -25558,7 +25558,7 @@
         <v>253.6</v>
       </c>
       <c r="G614">
-        <v>286.4</v>
+        <v>287.4</v>
       </c>
       <c r="H614">
         <v>253.4</v>
@@ -25581,7 +25581,7 @@
     </row>
     <row r="615" spans="1:13">
       <c r="A615" s="1">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="B615">
         <v>253.3</v>
@@ -25599,7 +25599,7 @@
         <v>253.6</v>
       </c>
       <c r="G615">
-        <v>286.4</v>
+        <v>287.4</v>
       </c>
       <c r="H615">
         <v>253.4</v>
@@ -25622,7 +25622,7 @@
     </row>
     <row r="616" spans="1:13">
       <c r="A616" s="1">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="B616">
         <v>253.3</v>
@@ -25658,47 +25658,6 @@
         <v>253.2</v>
       </c>
       <c r="M616">
-        <v>282.3</v>
-      </c>
-    </row>
-    <row r="617" spans="1:13">
-      <c r="A617" s="1">
-        <v>46303</v>
-      </c>
-      <c r="B617">
-        <v>253.3</v>
-      </c>
-      <c r="C617">
-        <v>282.3</v>
-      </c>
-      <c r="D617">
-        <v>243.2</v>
-      </c>
-      <c r="E617">
-        <v>243.2</v>
-      </c>
-      <c r="F617">
-        <v>253.6</v>
-      </c>
-      <c r="G617">
-        <v>287.4</v>
-      </c>
-      <c r="H617">
-        <v>253.4</v>
-      </c>
-      <c r="I617">
-        <v>282.4</v>
-      </c>
-      <c r="J617">
-        <v>276.7</v>
-      </c>
-      <c r="K617">
-        <v>285.6</v>
-      </c>
-      <c r="L617">
-        <v>253.2</v>
-      </c>
-      <c r="M617">
         <v>282.3</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M616"/>
+  <dimension ref="A1:M617"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25637,7 +25637,7 @@
         <v>243.2</v>
       </c>
       <c r="F616">
-        <v>253.6</v>
+        <v>254.6</v>
       </c>
       <c r="G616">
         <v>287.4</v>
@@ -25649,15 +25649,56 @@
         <v>282.4</v>
       </c>
       <c r="J616">
-        <v>276.7</v>
+        <v>275.7</v>
       </c>
       <c r="K616">
-        <v>285.6</v>
+        <v>284.6</v>
       </c>
       <c r="L616">
         <v>253.2</v>
       </c>
       <c r="M616">
+        <v>282.3</v>
+      </c>
+    </row>
+    <row r="617" spans="1:13">
+      <c r="A617" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B617">
+        <v>253.3</v>
+      </c>
+      <c r="C617">
+        <v>282.3</v>
+      </c>
+      <c r="D617">
+        <v>241.2</v>
+      </c>
+      <c r="E617">
+        <v>241.2</v>
+      </c>
+      <c r="F617">
+        <v>254.6</v>
+      </c>
+      <c r="G617">
+        <v>287.4</v>
+      </c>
+      <c r="H617">
+        <v>253.4</v>
+      </c>
+      <c r="I617">
+        <v>282.4</v>
+      </c>
+      <c r="J617">
+        <v>275.7</v>
+      </c>
+      <c r="K617">
+        <v>284.6</v>
+      </c>
+      <c r="L617">
+        <v>253.2</v>
+      </c>
+      <c r="M617">
         <v>282.3</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M617"/>
+  <dimension ref="A1:M618"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25702,6 +25702,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="618" spans="1:13">
+      <c r="A618" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B618">
+        <v>253.3</v>
+      </c>
+      <c r="C618">
+        <v>282.3</v>
+      </c>
+      <c r="D618">
+        <v>241.2</v>
+      </c>
+      <c r="E618">
+        <v>241.2</v>
+      </c>
+      <c r="F618">
+        <v>254.6</v>
+      </c>
+      <c r="G618">
+        <v>287.4</v>
+      </c>
+      <c r="H618">
+        <v>253.4</v>
+      </c>
+      <c r="I618">
+        <v>282.4</v>
+      </c>
+      <c r="J618">
+        <v>275.7</v>
+      </c>
+      <c r="K618">
+        <v>284.6</v>
+      </c>
+      <c r="L618">
+        <v>253.2</v>
+      </c>
+      <c r="M618">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25581,7 +25581,7 @@
     </row>
     <row r="615" spans="1:13">
       <c r="A615" s="1">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B615">
         <v>253.3</v>
@@ -25596,7 +25596,7 @@
         <v>243.2</v>
       </c>
       <c r="F615">
-        <v>253.6</v>
+        <v>254.6</v>
       </c>
       <c r="G615">
         <v>287.4</v>
@@ -25608,10 +25608,10 @@
         <v>282.4</v>
       </c>
       <c r="J615">
-        <v>276.7</v>
+        <v>275.7</v>
       </c>
       <c r="K615">
-        <v>285.6</v>
+        <v>284.6</v>
       </c>
       <c r="L615">
         <v>253.2</v>
@@ -25622,7 +25622,7 @@
     </row>
     <row r="616" spans="1:13">
       <c r="A616" s="1">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B616">
         <v>253.3</v>
@@ -25631,10 +25631,10 @@
         <v>282.3</v>
       </c>
       <c r="D616">
-        <v>243.2</v>
+        <v>241.2</v>
       </c>
       <c r="E616">
-        <v>243.2</v>
+        <v>241.2</v>
       </c>
       <c r="F616">
         <v>254.6</v>
@@ -25663,7 +25663,7 @@
     </row>
     <row r="617" spans="1:13">
       <c r="A617" s="1">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="B617">
         <v>253.3</v>
@@ -25704,7 +25704,7 @@
     </row>
     <row r="618" spans="1:13">
       <c r="A618" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B618">
         <v>253.3</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M618"/>
+  <dimension ref="A1:M619"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25743,6 +25743,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="619" spans="1:13">
+      <c r="A619" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B619">
+        <v>253.3</v>
+      </c>
+      <c r="C619">
+        <v>282.3</v>
+      </c>
+      <c r="D619">
+        <v>241.2</v>
+      </c>
+      <c r="E619">
+        <v>241.2</v>
+      </c>
+      <c r="F619">
+        <v>254.6</v>
+      </c>
+      <c r="G619">
+        <v>287.4</v>
+      </c>
+      <c r="H619">
+        <v>253.4</v>
+      </c>
+      <c r="I619">
+        <v>282.4</v>
+      </c>
+      <c r="J619">
+        <v>275.7</v>
+      </c>
+      <c r="K619">
+        <v>284.6</v>
+      </c>
+      <c r="L619">
+        <v>253.2</v>
+      </c>
+      <c r="M619">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M619"/>
+  <dimension ref="A1:M620"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25784,6 +25784,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="620" spans="1:13">
+      <c r="A620" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B620">
+        <v>253.3</v>
+      </c>
+      <c r="C620">
+        <v>282.3</v>
+      </c>
+      <c r="D620">
+        <v>241.2</v>
+      </c>
+      <c r="E620">
+        <v>241.2</v>
+      </c>
+      <c r="F620">
+        <v>254.6</v>
+      </c>
+      <c r="G620">
+        <v>287.4</v>
+      </c>
+      <c r="H620">
+        <v>253.4</v>
+      </c>
+      <c r="I620">
+        <v>282.4</v>
+      </c>
+      <c r="J620">
+        <v>275.7</v>
+      </c>
+      <c r="K620">
+        <v>284.6</v>
+      </c>
+      <c r="L620">
+        <v>253.2</v>
+      </c>
+      <c r="M620">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25663,7 +25663,7 @@
     </row>
     <row r="617" spans="1:13">
       <c r="A617" s="1">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B617">
         <v>253.3</v>
@@ -25704,7 +25704,7 @@
     </row>
     <row r="618" spans="1:13">
       <c r="A618" s="1">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B618">
         <v>253.3</v>
@@ -25745,7 +25745,7 @@
     </row>
     <row r="619" spans="1:13">
       <c r="A619" s="1">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B619">
         <v>253.3</v>
@@ -25786,7 +25786,7 @@
     </row>
     <row r="620" spans="1:13">
       <c r="A620" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B620">
         <v>253.3</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M620"/>
+  <dimension ref="A1:M621"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25825,6 +25825,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="621" spans="1:13">
+      <c r="A621" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B621">
+        <v>253.3</v>
+      </c>
+      <c r="C621">
+        <v>282.3</v>
+      </c>
+      <c r="D621">
+        <v>241.2</v>
+      </c>
+      <c r="E621">
+        <v>241.2</v>
+      </c>
+      <c r="F621">
+        <v>254.6</v>
+      </c>
+      <c r="G621">
+        <v>287.4</v>
+      </c>
+      <c r="H621">
+        <v>253.4</v>
+      </c>
+      <c r="I621">
+        <v>282.4</v>
+      </c>
+      <c r="J621">
+        <v>275.7</v>
+      </c>
+      <c r="K621">
+        <v>284.6</v>
+      </c>
+      <c r="L621">
+        <v>253.2</v>
+      </c>
+      <c r="M621">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M621"/>
+  <dimension ref="A1:M622"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25866,6 +25866,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="622" spans="1:13">
+      <c r="A622" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B622">
+        <v>253.3</v>
+      </c>
+      <c r="C622">
+        <v>282.3</v>
+      </c>
+      <c r="D622">
+        <v>241.2</v>
+      </c>
+      <c r="E622">
+        <v>241.2</v>
+      </c>
+      <c r="F622">
+        <v>254.6</v>
+      </c>
+      <c r="G622">
+        <v>287.4</v>
+      </c>
+      <c r="H622">
+        <v>253.4</v>
+      </c>
+      <c r="I622">
+        <v>282.4</v>
+      </c>
+      <c r="J622">
+        <v>275.7</v>
+      </c>
+      <c r="K622">
+        <v>284.6</v>
+      </c>
+      <c r="L622">
+        <v>253.2</v>
+      </c>
+      <c r="M622">
+        <v>282.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -25745,7 +25745,7 @@
     </row>
     <row r="619" spans="1:13">
       <c r="A619" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B619">
         <v>253.3</v>
@@ -25786,7 +25786,7 @@
     </row>
     <row r="620" spans="1:13">
       <c r="A620" s="1">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B620">
         <v>253.3</v>
@@ -25827,7 +25827,7 @@
     </row>
     <row r="621" spans="1:13">
       <c r="A621" s="1">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B621">
         <v>253.3</v>
@@ -25868,7 +25868,7 @@
     </row>
     <row r="622" spans="1:13">
       <c r="A622" s="1">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B622">
         <v>253.3</v>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M622"/>
+  <dimension ref="A1:M623"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25907,6 +25907,47 @@
         <v>282.3</v>
       </c>
     </row>
+    <row r="623" spans="1:13">
+      <c r="A623" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B623">
+        <v>253.3</v>
+      </c>
+      <c r="C623">
+        <v>284.3</v>
+      </c>
+      <c r="D623">
+        <v>241.2</v>
+      </c>
+      <c r="E623">
+        <v>241.2</v>
+      </c>
+      <c r="F623">
+        <v>254.6</v>
+      </c>
+      <c r="G623">
+        <v>287.4</v>
+      </c>
+      <c r="H623">
+        <v>255.4</v>
+      </c>
+      <c r="I623">
+        <v>284.4</v>
+      </c>
+      <c r="J623">
+        <v>277.7</v>
+      </c>
+      <c r="K623">
+        <v>286.6</v>
+      </c>
+      <c r="L623">
+        <v>253.2</v>
+      </c>
+      <c r="M623">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M623"/>
+  <dimension ref="A1:M624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25948,6 +25948,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="624" spans="1:13">
+      <c r="A624" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B624">
+        <v>253.3</v>
+      </c>
+      <c r="C624">
+        <v>284.3</v>
+      </c>
+      <c r="D624">
+        <v>241.2</v>
+      </c>
+      <c r="E624">
+        <v>241.2</v>
+      </c>
+      <c r="F624">
+        <v>254.6</v>
+      </c>
+      <c r="G624">
+        <v>287.4</v>
+      </c>
+      <c r="H624">
+        <v>255.4</v>
+      </c>
+      <c r="I624">
+        <v>284.4</v>
+      </c>
+      <c r="J624">
+        <v>277.7</v>
+      </c>
+      <c r="K624">
+        <v>286.6</v>
+      </c>
+      <c r="L624">
+        <v>253.2</v>
+      </c>
+      <c r="M624">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M624"/>
+  <dimension ref="A1:M623"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25827,13 +25827,13 @@
     </row>
     <row r="621" spans="1:13">
       <c r="A621" s="1">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="B621">
         <v>253.3</v>
       </c>
       <c r="C621">
-        <v>282.3</v>
+        <v>284.3</v>
       </c>
       <c r="D621">
         <v>241.2</v>
@@ -25848,39 +25848,39 @@
         <v>287.4</v>
       </c>
       <c r="H621">
-        <v>253.4</v>
+        <v>255.4</v>
       </c>
       <c r="I621">
-        <v>282.4</v>
+        <v>284.4</v>
       </c>
       <c r="J621">
-        <v>275.7</v>
+        <v>277.7</v>
       </c>
       <c r="K621">
-        <v>284.6</v>
+        <v>286.6</v>
       </c>
       <c r="L621">
         <v>253.2</v>
       </c>
       <c r="M621">
-        <v>282.3</v>
+        <v>284.3</v>
       </c>
     </row>
     <row r="622" spans="1:13">
       <c r="A622" s="1">
-        <v>46313</v>
+        <v>46315</v>
       </c>
       <c r="B622">
-        <v>253.3</v>
+        <v>255.3</v>
       </c>
       <c r="C622">
-        <v>282.3</v>
+        <v>284.3</v>
       </c>
       <c r="D622">
-        <v>241.2</v>
+        <v>242.4</v>
       </c>
       <c r="E622">
-        <v>241.2</v>
+        <v>242.4</v>
       </c>
       <c r="F622">
         <v>254.6</v>
@@ -25889,39 +25889,39 @@
         <v>287.4</v>
       </c>
       <c r="H622">
-        <v>253.4</v>
+        <v>255.4</v>
       </c>
       <c r="I622">
-        <v>282.4</v>
+        <v>284.4</v>
       </c>
       <c r="J622">
-        <v>275.7</v>
+        <v>277.7</v>
       </c>
       <c r="K622">
-        <v>284.6</v>
+        <v>286.6</v>
       </c>
       <c r="L622">
-        <v>253.2</v>
+        <v>254.5</v>
       </c>
       <c r="M622">
-        <v>282.3</v>
+        <v>284.3</v>
       </c>
     </row>
     <row r="623" spans="1:13">
       <c r="A623" s="1">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="B623">
-        <v>253.3</v>
+        <v>254.5</v>
       </c>
       <c r="C623">
         <v>284.3</v>
       </c>
       <c r="D623">
-        <v>241.2</v>
+        <v>242.4</v>
       </c>
       <c r="E623">
-        <v>241.2</v>
+        <v>242.4</v>
       </c>
       <c r="F623">
         <v>254.6</v>
@@ -25942,50 +25942,9 @@
         <v>286.6</v>
       </c>
       <c r="L623">
-        <v>253.2</v>
+        <v>254.4</v>
       </c>
       <c r="M623">
-        <v>284.3</v>
-      </c>
-    </row>
-    <row r="624" spans="1:13">
-      <c r="A624" s="1">
-        <v>46315</v>
-      </c>
-      <c r="B624">
-        <v>253.3</v>
-      </c>
-      <c r="C624">
-        <v>284.3</v>
-      </c>
-      <c r="D624">
-        <v>241.2</v>
-      </c>
-      <c r="E624">
-        <v>241.2</v>
-      </c>
-      <c r="F624">
-        <v>254.6</v>
-      </c>
-      <c r="G624">
-        <v>287.4</v>
-      </c>
-      <c r="H624">
-        <v>255.4</v>
-      </c>
-      <c r="I624">
-        <v>284.4</v>
-      </c>
-      <c r="J624">
-        <v>277.7</v>
-      </c>
-      <c r="K624">
-        <v>286.6</v>
-      </c>
-      <c r="L624">
-        <v>253.2</v>
-      </c>
-      <c r="M624">
         <v>284.3</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M623"/>
+  <dimension ref="A1:M624"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25948,6 +25948,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="624" spans="1:13">
+      <c r="A624" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B624">
+        <v>254.5</v>
+      </c>
+      <c r="C624">
+        <v>283.5</v>
+      </c>
+      <c r="D624">
+        <v>242.4</v>
+      </c>
+      <c r="E624">
+        <v>242.4</v>
+      </c>
+      <c r="F624">
+        <v>255.6</v>
+      </c>
+      <c r="G624">
+        <v>288.4</v>
+      </c>
+      <c r="H624">
+        <v>255.4</v>
+      </c>
+      <c r="I624">
+        <v>284.4</v>
+      </c>
+      <c r="J624">
+        <v>277.7</v>
+      </c>
+      <c r="K624">
+        <v>286.6</v>
+      </c>
+      <c r="L624">
+        <v>254.4</v>
+      </c>
+      <c r="M624">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M624"/>
+  <dimension ref="A1:M625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25989,6 +25989,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="625" spans="1:13">
+      <c r="A625" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B625">
+        <v>254.5</v>
+      </c>
+      <c r="C625">
+        <v>283.5</v>
+      </c>
+      <c r="D625">
+        <v>242.4</v>
+      </c>
+      <c r="E625">
+        <v>242.4</v>
+      </c>
+      <c r="F625">
+        <v>255.6</v>
+      </c>
+      <c r="G625">
+        <v>288.4</v>
+      </c>
+      <c r="H625">
+        <v>255.4</v>
+      </c>
+      <c r="I625">
+        <v>284.4</v>
+      </c>
+      <c r="J625">
+        <v>277.7</v>
+      </c>
+      <c r="K625">
+        <v>286.6</v>
+      </c>
+      <c r="L625">
+        <v>254.4</v>
+      </c>
+      <c r="M625">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M625"/>
+  <dimension ref="A1:M626"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -25997,7 +25997,7 @@
         <v>254.5</v>
       </c>
       <c r="C625">
-        <v>283.5</v>
+        <v>284.3</v>
       </c>
       <c r="D625">
         <v>242.4</v>
@@ -26027,6 +26027,47 @@
         <v>254.4</v>
       </c>
       <c r="M625">
+        <v>284.3</v>
+      </c>
+    </row>
+    <row r="626" spans="1:13">
+      <c r="A626" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B626">
+        <v>254.5</v>
+      </c>
+      <c r="C626">
+        <v>284.3</v>
+      </c>
+      <c r="D626">
+        <v>242.4</v>
+      </c>
+      <c r="E626">
+        <v>242.4</v>
+      </c>
+      <c r="F626">
+        <v>255.6</v>
+      </c>
+      <c r="G626">
+        <v>288.4</v>
+      </c>
+      <c r="H626">
+        <v>255.4</v>
+      </c>
+      <c r="I626">
+        <v>284.4</v>
+      </c>
+      <c r="J626">
+        <v>277.7</v>
+      </c>
+      <c r="K626">
+        <v>286.6</v>
+      </c>
+      <c r="L626">
+        <v>254.4</v>
+      </c>
+      <c r="M626">
         <v>284.3</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M626"/>
+  <dimension ref="A1:M627"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26071,6 +26071,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="627" spans="1:13">
+      <c r="A627" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B627">
+        <v>254.5</v>
+      </c>
+      <c r="C627">
+        <v>284.3</v>
+      </c>
+      <c r="D627">
+        <v>242.4</v>
+      </c>
+      <c r="E627">
+        <v>242.4</v>
+      </c>
+      <c r="F627">
+        <v>255.6</v>
+      </c>
+      <c r="G627">
+        <v>288.4</v>
+      </c>
+      <c r="H627">
+        <v>255.4</v>
+      </c>
+      <c r="I627">
+        <v>284.4</v>
+      </c>
+      <c r="J627">
+        <v>277.7</v>
+      </c>
+      <c r="K627">
+        <v>286.6</v>
+      </c>
+      <c r="L627">
+        <v>254.4</v>
+      </c>
+      <c r="M627">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M627"/>
+  <dimension ref="A1:M628"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26112,6 +26112,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="628" spans="1:13">
+      <c r="A628" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B628">
+        <v>255.3</v>
+      </c>
+      <c r="C628">
+        <v>284.3</v>
+      </c>
+      <c r="D628">
+        <v>243.2</v>
+      </c>
+      <c r="E628">
+        <v>243.2</v>
+      </c>
+      <c r="F628">
+        <v>256.6</v>
+      </c>
+      <c r="G628">
+        <v>289.4</v>
+      </c>
+      <c r="H628">
+        <v>255.4</v>
+      </c>
+      <c r="I628">
+        <v>284.4</v>
+      </c>
+      <c r="J628">
+        <v>277.7</v>
+      </c>
+      <c r="K628">
+        <v>286.6</v>
+      </c>
+      <c r="L628">
+        <v>255.2</v>
+      </c>
+      <c r="M628">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M628"/>
+  <dimension ref="A1:M629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26153,6 +26153,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="629" spans="1:13">
+      <c r="A629" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B629">
+        <v>255.3</v>
+      </c>
+      <c r="C629">
+        <v>284.3</v>
+      </c>
+      <c r="D629">
+        <v>243.2</v>
+      </c>
+      <c r="E629">
+        <v>243.2</v>
+      </c>
+      <c r="F629">
+        <v>256.6</v>
+      </c>
+      <c r="G629">
+        <v>289.4</v>
+      </c>
+      <c r="H629">
+        <v>255.4</v>
+      </c>
+      <c r="I629">
+        <v>284.4</v>
+      </c>
+      <c r="J629">
+        <v>277.7</v>
+      </c>
+      <c r="K629">
+        <v>286.6</v>
+      </c>
+      <c r="L629">
+        <v>255.2</v>
+      </c>
+      <c r="M629">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M629"/>
+  <dimension ref="A1:M628"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26032,25 +26032,25 @@
     </row>
     <row r="626" spans="1:13">
       <c r="A626" s="1">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="B626">
-        <v>254.5</v>
+        <v>255.3</v>
       </c>
       <c r="C626">
         <v>284.3</v>
       </c>
       <c r="D626">
-        <v>242.4</v>
+        <v>243.2</v>
       </c>
       <c r="E626">
-        <v>242.4</v>
+        <v>243.2</v>
       </c>
       <c r="F626">
-        <v>255.6</v>
+        <v>256.6</v>
       </c>
       <c r="G626">
-        <v>288.4</v>
+        <v>289.4</v>
       </c>
       <c r="H626">
         <v>255.4</v>
@@ -26065,7 +26065,7 @@
         <v>286.6</v>
       </c>
       <c r="L626">
-        <v>254.4</v>
+        <v>255.2</v>
       </c>
       <c r="M626">
         <v>284.3</v>
@@ -26073,25 +26073,25 @@
     </row>
     <row r="627" spans="1:13">
       <c r="A627" s="1">
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="B627">
-        <v>254.5</v>
+        <v>255.3</v>
       </c>
       <c r="C627">
         <v>284.3</v>
       </c>
       <c r="D627">
-        <v>242.4</v>
+        <v>243.2</v>
       </c>
       <c r="E627">
-        <v>242.4</v>
+        <v>243.2</v>
       </c>
       <c r="F627">
-        <v>255.6</v>
+        <v>256.6</v>
       </c>
       <c r="G627">
-        <v>288.4</v>
+        <v>289.4</v>
       </c>
       <c r="H627">
         <v>255.4</v>
@@ -26106,7 +26106,7 @@
         <v>286.6</v>
       </c>
       <c r="L627">
-        <v>254.4</v>
+        <v>255.2</v>
       </c>
       <c r="M627">
         <v>284.3</v>
@@ -26114,7 +26114,7 @@
     </row>
     <row r="628" spans="1:13">
       <c r="A628" s="1">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="B628">
         <v>255.3</v>
@@ -26150,47 +26150,6 @@
         <v>255.2</v>
       </c>
       <c r="M628">
-        <v>284.3</v>
-      </c>
-    </row>
-    <row r="629" spans="1:13">
-      <c r="A629" s="1">
-        <v>46322</v>
-      </c>
-      <c r="B629">
-        <v>255.3</v>
-      </c>
-      <c r="C629">
-        <v>284.3</v>
-      </c>
-      <c r="D629">
-        <v>243.2</v>
-      </c>
-      <c r="E629">
-        <v>243.2</v>
-      </c>
-      <c r="F629">
-        <v>256.6</v>
-      </c>
-      <c r="G629">
-        <v>289.4</v>
-      </c>
-      <c r="H629">
-        <v>255.4</v>
-      </c>
-      <c r="I629">
-        <v>284.4</v>
-      </c>
-      <c r="J629">
-        <v>277.7</v>
-      </c>
-      <c r="K629">
-        <v>286.6</v>
-      </c>
-      <c r="L629">
-        <v>255.2</v>
-      </c>
-      <c r="M629">
         <v>284.3</v>
       </c>
     </row>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M628"/>
+  <dimension ref="A1:M629"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26153,6 +26153,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="629" spans="1:13">
+      <c r="A629" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B629">
+        <v>255.3</v>
+      </c>
+      <c r="C629">
+        <v>284.3</v>
+      </c>
+      <c r="D629">
+        <v>243.2</v>
+      </c>
+      <c r="E629">
+        <v>243.2</v>
+      </c>
+      <c r="F629">
+        <v>256.6</v>
+      </c>
+      <c r="G629">
+        <v>289.4</v>
+      </c>
+      <c r="H629">
+        <v>255.4</v>
+      </c>
+      <c r="I629">
+        <v>284.4</v>
+      </c>
+      <c r="J629">
+        <v>277.7</v>
+      </c>
+      <c r="K629">
+        <v>286.6</v>
+      </c>
+      <c r="L629">
+        <v>255.2</v>
+      </c>
+      <c r="M629">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M629"/>
+  <dimension ref="A1:M630"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -26194,6 +26194,47 @@
         <v>284.3</v>
       </c>
     </row>
+    <row r="630" spans="1:13">
+      <c r="A630" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B630">
+        <v>255.3</v>
+      </c>
+      <c r="C630">
+        <v>284.3</v>
+      </c>
+      <c r="D630">
+        <v>243.2</v>
+      </c>
+      <c r="E630">
+        <v>243.2</v>
+      </c>
+      <c r="F630">
+        <v>256.6</v>
+      </c>
+      <c r="G630">
+        <v>289.4</v>
+      </c>
+      <c r="H630">
+        <v>255.4</v>
+      </c>
+      <c r="I630">
+        <v>284.4</v>
+      </c>
+      <c r="J630">
+        <v>277.7</v>
+      </c>
+      <c r="K630">
+        <v>286.6</v>
+      </c>
+      <c r="L630">
+        <v>255.2</v>
+      </c>
+      <c r="M630">
+        <v>284.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/min_max_dagverd.xlsx
+++ b/min_max_dagverd.xlsx
@@ -26073,7 +26073,7 @@
     </row>
     <row r="627" spans="1:13">
       <c r="A627" s="1">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="B627">
         <v>255.3</v>
@@ -26114,7 +26114,7 @@
     </row>
     <row r="628" spans="1:13">
       <c r="A628" s="1">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="B628">
         <v>255.3</v>
@@ -26155,7 +26155,7 @@
     </row>
     <row r="629" spans="1:13">
       <c r="A629" s="1">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="B629">
         <v>255.3</v>
@@ -26196,7 +26196,7 @@
     </row>
     <row r="630" spans="1:13">
       <c r="A630" s="1">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="B630">
         <v>255.3</v>
